--- a/docs/review/packs/chapter-3.10.xlsx
+++ b/docs/review/packs/chapter-3.10.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Expect a popliteus injury to remove an active restraint as well as a passive one.</t>
+          <t>Read an increase at 90 degrees as implicating the posterior cruciate.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Treat external rotation laxity as the finding that defines the corner injury and drives the operation, and the two angle comparison as the finding that defines its company.</t>
+          <t>Expect a popliteus injury to remove an active restraint as well as a passive one.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2058,12 +2058,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.10.3-P1</t>
+          <t>3.10.2-P3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>3.10.3</t>
+          <t>3.10.2</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Identify the avulsion site, since it affects whether repair is possible.</t>
+          <t>Accept that no routine instrument quantifies this laxity.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2083,22 +2083,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.10.3-P2</t>
+          <t>3.10.2-P4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.10.3</t>
+          <t>3.10.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Expect corner involvement alongside a significant injury.</t>
+          <t>Treat external rotation laxity as the finding that defines the corner injury and drives the operation, and the two angle comparison as the finding that defines its company.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2108,22 +2108,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.10.3-P3</t>
+          <t>3.10.2-P5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.10.3</t>
+          <t>3.10.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Place a reconstruction's femoral attachment proximal and posterior to the epicondyle.</t>
+          <t>Read the 30 and 90 degree comparison to establish what else is injured.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2133,12 +2133,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.10.3-P4</t>
+          <t>3.10.2-P6</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.10.3</t>
+          <t>3.10.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Treat this ligament as the easier half of a lateral reconstruction and the corner as the harder half.</t>
+          <t>Correct varus alignment where it would load a corner reconstruction.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2158,12 +2158,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.10.3-P5</t>
+          <t>3.10.2-P7</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.10.3</t>
+          <t>3.10.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Place the attachments anatomically, since they are identifiable here.</t>
+          <t>Accept that the rotatory component cannot be quantified clinically.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.10.3-P6</t>
+          <t>3.10.3-P1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Expect a chronic lateral laxity not to improve with time.</t>
+          <t>Identify the avulsion site, since it affects whether repair is possible.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2208,12 +2208,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.10.4-P1</t>
+          <t>3.10.3-P2</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.10.4</t>
+          <t>3.10.3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Treat it as a complex and name the component when discussing injury or reconstruction.</t>
+          <t>Expect corner involvement alongside a significant injury.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2233,12 +2233,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.10.4-P2</t>
+          <t>3.10.3-P3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3.10.4</t>
+          <t>3.10.3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Expect its loss to remove an active and a passive restraint in the same direction.</t>
+          <t>Place a reconstruction's femoral attachment proximal and posterior to the epicondyle.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2258,12 +2258,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.10.4-P3</t>
+          <t>3.10.3-P4</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.10.4</t>
+          <t>3.10.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Treat the complex as the structure that makes anatomic corner reconstruction a three component operation: the lateral collateral, the popliteus tendon and the popliteofibular ligament.</t>
+          <t>Treat this ligament as the easier half of a lateral reconstruction and the corner as the harder half.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2283,22 +2283,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.10.5-P1</t>
+          <t>3.10.3-P5</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.10.5</t>
+          <t>3.10.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Expect inconsistent demonstration on magnetic resonance imaging.</t>
+          <t>Place the attachments anatomically, since they are identifiable here.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2308,12 +2308,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.10.5-P2</t>
+          <t>3.10.3-P6</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.10.5</t>
+          <t>3.10.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Treat this ligament as the component whose reconstruction distinguishes an anatomic corner procedure from a tenodesis, and treat the fibular head as the crowded and fragile part of the operation.</t>
+          <t>Correct varus alignment where it would load the construct.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2333,12 +2333,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.10.5-P3</t>
+          <t>3.10.3-P7</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.10.5</t>
+          <t>3.10.3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Plan fibular fixation around the crowding and the bone quality.</t>
+          <t>Expect a chronic lateral laxity not to improve with time.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2358,12 +2358,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P1</t>
+          <t>3.10.4-P1</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Assess varus, external rotation and posterior laxity together when a corner injury is suspected.</t>
+          <t>Treat it as a complex and name the component when discussing injury or reconstruction.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2383,12 +2383,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P2</t>
+          <t>3.10.4-P2</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Examine under anaesthetic, since the findings are subtle and the imaging inconsistent.</t>
+          <t>Expect its loss to remove an active and a passive restraint in the same direction.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2408,12 +2408,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P3</t>
+          <t>3.10.4-P3</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Expect apportionment within the corner to be less settled than between corner and cruciate.</t>
+          <t>Read apportionment variation as reflecting different sectioning of the complex.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2433,12 +2433,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P4</t>
+          <t>3.10.4-P4</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Treat the corner as the structure whose assessment belongs in every cruciate operation.</t>
+          <t>Treat the complex as the structure that makes anatomic corner reconstruction a three component operation: the lateral collateral, the popliteus tendon and the popliteofibular ligament.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2458,12 +2458,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P5</t>
+          <t>3.10.4-P5</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Assess the corner under anaesthetic in every cruciate reconstruction.</t>
+          <t>State that the muscle's active roles are not restored by a graft.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2483,12 +2483,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P6</t>
+          <t>3.10.4-P6</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Document peroneal nerve function before and after corner surgery.</t>
+          <t>Confirm tunnel positions on imaging, since the femoral origins are close together.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2508,12 +2508,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.10.6-P7</t>
+          <t>3.10.4-P7</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.10.6</t>
+          <t>3.10.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Expect a chronic corner injury not to improve without surgery.</t>
+          <t>Correct alignment, since the construct cannot carry a varus limb's load.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2533,12 +2533,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.10.7-P1</t>
+          <t>3.10.5-P1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.10.7</t>
+          <t>3.10.5</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Expect interpretation to be harder when both structures are badly injured.</t>
+          <t>Expect inconsistent demonstration on magnetic resonance imaging.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2558,12 +2558,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.10.7-P2</t>
+          <t>3.10.5-P2</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.10.7</t>
+          <t>3.10.5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Treat the dial test as the intraoperative check as well as the clinical one.</t>
+          <t>Treat this ligament as the component whose reconstruction distinguishes an anatomic corner procedure from a tenodesis, and treat the fibular head as the crowded and fragile part of the operation.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2583,12 +2583,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.10.7-P3</t>
+          <t>3.10.5-P3</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.10.7</t>
+          <t>3.10.5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Use it as an intraoperative check rather than as a comparative outcome measure.</t>
+          <t>Plan fibular fixation around the crowding and the bone quality.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2608,12 +2608,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P1</t>
+          <t>3.10.6-P1</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Plan the femoral tunnels to avoid convergence and preserve the bone bridge.</t>
+          <t>Assess varus, external rotation and posterior laxity together when a corner injury is suspected.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2633,12 +2633,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P2</t>
+          <t>3.10.6-P2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Measure the coronal result radiographically and the rotational one by dial test.</t>
+          <t>Read a large posterior laxity as suggesting corner involvement.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2658,22 +2658,22 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P3</t>
+          <t>3.10.6-P3</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat the reconstruction as a construct in an environment, where the environment is varus alignment and the cruciates.</t>
+          <t>Examine under anaesthetic, since the findings are subtle and the imaging inconsistent.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2683,22 +2683,22 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P4</t>
+          <t>3.10.6-P4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Document peroneal nerve function before surgery and after.</t>
+          <t>Expect apportionment within the corner to be less settled than between corner and cruciate.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2708,12 +2708,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P5</t>
+          <t>3.10.6-P5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Check the dial test under anaesthetic before leaving theatre.</t>
+          <t>Treat the corner as the structure whose assessment belongs in every cruciate operation.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2733,22 +2733,22 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P6</t>
+          <t>3.10.6-P6</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel trajectories before theatre in a multiligament corner reconstruction.</t>
+          <t>Assess the corner under anaesthetic in every cruciate reconstruction.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2758,22 +2758,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P7</t>
+          <t>3.10.6-P7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Consider staging where graft, time or soft tissues will not allow one sitting.</t>
+          <t>Correct varus alignment where a corner reconstruction would otherwise be loaded.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2783,22 +2783,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P8</t>
+          <t>3.10.6-P8</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Consider an inlay for the posterior cruciate to free tibial tunnel space.</t>
+          <t>Document peroneal nerve function before and after corner surgery.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2808,22 +2808,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P1</t>
+          <t>3.10.6-P9</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.10.9</t>
+          <t>3.10.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment, since varus loads both.</t>
+          <t>Expect a chronic corner injury not to improve without surgery.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2833,22 +2833,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P2</t>
+          <t>3.10.7-P1</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.10.9</t>
+          <t>3.10.7</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Treat this as the combination where the environment, the structures and the alignment all have to be addressed, and where a single sitting may not be possible.</t>
+          <t>Compare with the uninjured side rather than against an absolute figure.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2858,22 +2858,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P3</t>
+          <t>3.10.7-P2</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.10.9</t>
+          <t>3.10.7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnels to avoid convergence, considering an inlay for the cruciate.</t>
+          <t>Repeat under anaesthetic where the finding will change the operation.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2883,31 +2883,431 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P4</t>
+          <t>3.10.7-P3</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.10.9</t>
+          <t>3.10.7</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Measure both components before and after, by their own methods.</t>
+          <t>Expect interpretation to be harder when both structures are badly injured.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>3.10.7-P4</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>3.10.7</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Treat the dial test as the intraoperative check as well as the clinical one.</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>3.10.7-P5</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>3.10.7</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Use it as an intraoperative check rather than as a comparative outcome measure.</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P1</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Plan the femoral tunnels to avoid convergence and preserve the bone bridge.</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P2</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Measure the coronal result radiographically and the rotational one by dial test.</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P3</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Treat the reconstruction as a construct in an environment, where the environment is varus alignment and the cruciates.</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P4</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Correct varus alignment before or with a chronic corner reconstruction.</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P5</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Document peroneal nerve function before surgery and after.</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P6</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Check the dial test under anaesthetic before leaving theatre.</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P7</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Plan tunnel trajectories before theatre in a multiligament corner reconstruction.</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P8</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Correct the deformity that is driving the failure first.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P9</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Consider staging where graft, time or soft tissues will not allow one sitting.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8-P10</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>3.10.8</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Consider an inlay for the posterior cruciate to free tibial tunnel space.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9-P1</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Measure alignment, since varus loads both.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9-P2</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Treat this as the combination where the environment, the structures and the alignment all have to be addressed, and where a single sitting may not be possible.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9-P3</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Plan tunnels to avoid convergence, considering an inlay for the cruciate.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9-P4</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Measure both components before and after, by their own methods.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3538,7 +3938,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>43</f>
+        <f>59</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3553,7 +3953,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E45,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E61,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3583,7 +3983,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E45,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E61,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3595,7 +3995,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E45,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E61,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -3607,7 +4007,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E45,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E61,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -3619,7 +4019,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E45,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E61,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.10.xlsx
+++ b/docs/review/packs/chapter-3.10.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2958,22 +2958,22 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P1</t>
+          <t>3.10.7-P6</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.10.8</t>
+          <t>3.10.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Plan the femoral tunnels to avoid convergence and preserve the bone bridge.</t>
+          <t>Record both angles and the side to side difference.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P2</t>
+          <t>3.10.8-P1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Measure the coronal result radiographically and the rotational one by dial test.</t>
+          <t>Plan the femoral tunnels to avoid convergence and preserve the bone bridge.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3008,7 +3008,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P3</t>
+          <t>3.10.8-P2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Treat the reconstruction as a construct in an environment, where the environment is varus alignment and the cruciates.</t>
+          <t>Measure the coronal result radiographically and the rotational one by dial test.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P4</t>
+          <t>3.10.8-P3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Correct varus alignment before or with a chronic corner reconstruction.</t>
+          <t>Treat the reconstruction as a construct in an environment, where the environment is varus alignment and the cruciates.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P5</t>
+          <t>3.10.8-P4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Document peroneal nerve function before surgery and after.</t>
+          <t>Correct varus alignment before or with a chronic corner reconstruction.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3083,7 +3083,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P6</t>
+          <t>3.10.8-P5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Check the dial test under anaesthetic before leaving theatre.</t>
+          <t>Document peroneal nerve function before surgery and after.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3108,7 +3108,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P7</t>
+          <t>3.10.8-P6</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnel trajectories before theatre in a multiligament corner reconstruction.</t>
+          <t>Check the dial test under anaesthetic before leaving theatre.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P8</t>
+          <t>3.10.8-P7</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Correct the deformity that is driving the failure first.</t>
+          <t>Plan tunnel trajectories before theatre in a multiligament corner reconstruction.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3158,7 +3158,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P9</t>
+          <t>3.10.8-P8</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Consider staging where graft, time or soft tissues will not allow one sitting.</t>
+          <t>Correct the deformity that is driving the failure first.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.10.8-P10</t>
+          <t>3.10.8-P9</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Consider an inlay for the posterior cruciate to free tibial tunnel space.</t>
+          <t>Consider staging where graft, time or soft tissues will not allow one sitting.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3208,22 +3208,22 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P1</t>
+          <t>3.10.8-P10</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.10.9</t>
+          <t>3.10.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment, since varus loads both.</t>
+          <t>Consider an inlay for the posterior cruciate to free tibial tunnel space.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P2</t>
+          <t>3.10.9-P1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Treat this as the combination where the environment, the structures and the alignment all have to be addressed, and where a single sitting may not be possible.</t>
+          <t>Measure alignment, since varus loads both.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P3</t>
+          <t>3.10.9-P2</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Plan tunnels to avoid convergence, considering an inlay for the cruciate.</t>
+          <t>Treat this as the combination where the environment, the structures and the alignment all have to be addressed, and where a single sitting may not be possible.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.10.9-P4</t>
+          <t>3.10.9-P3</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3298,16 +3298,66 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Measure both components before and after, by their own methods.</t>
+          <t>Plan tunnels to avoid convergence, considering an inlay for the cruciate.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9-P4</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Measure both components before and after, by their own methods.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9-P5</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.10.9</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Counsel that outcomes in this combination are worse than in isolated injury.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3938,7 +3988,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>59</f>
+        <f>61</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -3953,7 +4003,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E61,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E63,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -3983,7 +4033,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E61,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E63,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -3995,7 +4045,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E61,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E63,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -4007,7 +4057,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E61,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E63,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -4019,7 +4069,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E61,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E63,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
